--- a/reports/variance_pack_2026-08.xlsx
+++ b/reports/variance_pack_2026-08.xlsx
@@ -680,13 +680,13 @@
         <v>0.0448282596803243</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>395020.0509557571</v>
+        <v>395020.0509557616</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>303866.4291901612</v>
+        <v>303866.4291901646</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>486173.672721353</v>
+        <v>486173.6727213585</v>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
@@ -723,13 +723,13 @@
         <v>-0.07830802775820045</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>792827.4271364984</v>
+        <v>792827.4271364987</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>747450.562612574</v>
+        <v>747450.5626125523</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>838204.2916604228</v>
+        <v>838204.2916604452</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         <v>469495.24</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>420493.7043095912</v>
+        <v>420493.7043095827</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>518496.7756904088</v>
+        <v>518496.7756904173</v>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         <v>155032.2310451691</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>72786.62044620622</v>
+        <v>72786.62044620635</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>237277.841644132</v>
+        <v>237277.8416441319</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         <v>-0.08620652940640688</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>1501656.193898288</v>
+        <v>1501650.892563412</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>1382439.134181864</v>
+        <v>1382431.279703259</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1620873.253614711</v>
+        <v>1620870.505423565</v>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
@@ -898,10 +898,10 @@
         <v>5964319.588486933</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>5714320.541844958</v>
+        <v>5714320.541844915</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>6214318.635128908</v>
+        <v>6214318.635128952</v>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
@@ -1374,16 +1374,16 @@
         <v>3835106.48</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>2050977.337103771</v>
+        <v>2050977.337103397</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>5886083.817103771</v>
+        <v>5886083.817103397</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>6050772.48</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>-164688.662896229</v>
+        <v>-164688.6628966024</v>
       </c>
     </row>
     <row r="6">
@@ -1428,16 +1428,16 @@
         <v>1329769.14</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>996020.4606608009</v>
+        <v>996020.4606607988</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2325789.600660801</v>
+        <v>2325789.600660799</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>3306890.82</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-981101.2193391989</v>
+        <v>-981101.2193392008</v>
       </c>
     </row>
     <row r="8">
@@ -1455,16 +1455,16 @@
         <v>1316036.09</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>742293.7866580297</v>
+        <v>742293.7866580579</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2058329.87665803</v>
+        <v>2058329.876658058</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>2002180.56</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>56149.3166580298</v>
+        <v>56149.31665805797</v>
       </c>
     </row>
     <row r="9">
@@ -1482,16 +1482,16 @@
         <v>581292.79</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>133883.660321754</v>
+        <v>133883.6603217578</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>715176.450321754</v>
+        <v>715176.4503217579</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>327602.52</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>387573.930321754</v>
+        <v>387573.9303217579</v>
       </c>
     </row>
     <row r="10">
@@ -1509,16 +1509,16 @@
         <v>1037069.78</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>594327.1133584343</v>
+        <v>594327.1133585527</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>1631396.893358434</v>
+        <v>1631396.893358553</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1487038.5</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>144358.3933584343</v>
+        <v>144358.3933585528</v>
       </c>
     </row>
     <row r="11">
@@ -1536,7 +1536,7 @@
         <v>1188753.1</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>630418.1976149178</v>
+        <v>630418.197614918</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>1819171.297614918</v>
@@ -1545,7 +1545,7 @@
         <v>1510361.92</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>308809.3776149179</v>
+        <v>308809.3776149182</v>
       </c>
     </row>
     <row r="12">
@@ -1590,16 +1590,16 @@
         <v>2267507.96</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1656841.82663635</v>
+        <v>1656841.826636346</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>3924349.78663635</v>
+        <v>3924349.786636346</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>3840693.77</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>83656.01663634973</v>
+        <v>83656.016636346</v>
       </c>
     </row>
     <row r="14">
@@ -1644,16 +1644,16 @@
         <v>2131870.47</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1113332.849803169</v>
+        <v>1113332.849803158</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>3245203.319803169</v>
+        <v>3245203.319803158</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>3205113.2</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>40090.11980316928</v>
+        <v>40090.11980315764</v>
       </c>
     </row>
     <row r="16">
@@ -1671,16 +1671,16 @@
         <v>11646249.62</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>6140315.193825455</v>
+        <v>6140118.898362631</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>17786564.81382546</v>
+        <v>17786368.51836263</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>19147215.11</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>-1360650.296174541</v>
+        <v>-1360846.591637366</v>
       </c>
     </row>
     <row r="17">
@@ -1725,16 +1725,16 @@
         <v>2674900.71</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1399033.290616464</v>
+        <v>1399033.290616463</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>4073934.000616464</v>
+        <v>4073934.000616463</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>4476147.62</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>-402213.6193835363</v>
+        <v>-402213.6193835367</v>
       </c>
     </row>
     <row r="19">
@@ -1752,7 +1752,7 @@
         <v>1754956.39</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>887834.5045890471</v>
+        <v>887834.5045890469</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>2642790.894589047</v>
@@ -1779,16 +1779,16 @@
         <v>1720395.23</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>868442.1967758432</v>
+        <v>868442.196775842</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2588837.426775843</v>
+        <v>2588837.426775842</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>2954942.06</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>-366104.6332241572</v>
+        <v>-366104.6332241581</v>
       </c>
     </row>
     <row r="21">
@@ -1806,16 +1806,16 @@
         <v>5983806.13</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>3214492.434545761</v>
+        <v>3214492.434545765</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>9198298.564545762</v>
+        <v>9198298.564545766</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>9871045.23</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>-672746.6654542387</v>
+        <v>-672746.6654542349</v>
       </c>
     </row>
     <row r="22">
@@ -1833,16 +1833,16 @@
         <v>1127977.86</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>666531.6435369272</v>
+        <v>666531.643536928</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>1794509.503536927</v>
+        <v>1794509.503536928</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>1661106.94</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>133402.5635369273</v>
+        <v>133402.563536928</v>
       </c>
     </row>
     <row r="23">
@@ -1887,16 +1887,16 @@
         <v>346922.18</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>171284.1383220756</v>
+        <v>171284.1383220731</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>518206.3183220756</v>
+        <v>518206.3183220731</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>578932.39</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>-60726.07167792437</v>
+        <v>-60726.07167792693</v>
       </c>
     </row>
     <row r="25">
@@ -1914,16 +1914,16 @@
         <v>174810.39</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>101025.9273889296</v>
+        <v>101025.9273889406</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>275836.3173889297</v>
+        <v>275836.3173889407</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>270264.69</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>5571.627388929657</v>
+        <v>5571.627388940658</v>
       </c>
     </row>
     <row r="26">
@@ -1941,16 +1941,16 @@
         <v>1510035.48</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>167780.2793624432</v>
+        <v>167781.7158303749</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>1677815.759362443</v>
+        <v>1677817.195830375</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>1699211.2</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>-21395.44063755684</v>
+        <v>-21394.004169625</v>
       </c>
     </row>
     <row r="27">
@@ -1968,16 +1968,16 @@
         <v>128265.45</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>67410.53748287656</v>
+        <v>66030.45584340673</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>195675.9874828766</v>
+        <v>194295.9058434067</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>219606.58</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-23930.59251712341</v>
+        <v>-25310.67415659325</v>
       </c>
     </row>
     <row r="28">
@@ -1995,16 +1995,16 @@
         <v>20984.27</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>12679.92039912507</v>
+        <v>12679.9202871499</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>33664.19039912507</v>
+        <v>33664.1902871499</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>33808.07</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>-143.8796008749268</v>
+        <v>-143.8797128500955</v>
       </c>
     </row>
     <row r="29">
@@ -2049,16 +2049,16 @@
         <v>833695.67</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>356767.7350432953</v>
+        <v>356767.7276614694</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>1190463.405043295</v>
+        <v>1190463.397661469</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>1314296.54</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>-123833.1349567047</v>
+        <v>-123833.1423385306</v>
       </c>
     </row>
     <row r="31">
@@ -2076,16 +2076,16 @@
         <v>6845626.79</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>3433684.68332621</v>
+        <v>3433684.683326203</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>10279311.47332621</v>
+        <v>10279311.4733262</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>8750693.6</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>1528617.87332621</v>
+        <v>1528617.873326203</v>
       </c>
     </row>
   </sheetData>

--- a/reports/variance_pack_2026-08.xlsx
+++ b/reports/variance_pack_2026-08.xlsx
@@ -510,7 +510,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Altair Cloud, Inc. - Monthly Variance Pack</t>
+          <t>EZ Tech, Inc. - Monthly Variance Pack</t>
         </is>
       </c>
     </row>
@@ -680,13 +680,13 @@
         <v>0.0448282596803243</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>395020.0509557616</v>
+        <v>395020.0509557571</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>303866.4291901646</v>
+        <v>303866.4291901612</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>486173.6727213585</v>
+        <v>486173.672721353</v>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
@@ -723,13 +723,13 @@
         <v>-0.07830802775820045</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>792827.4271364987</v>
+        <v>792827.4271364984</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>747450.5626125523</v>
+        <v>747450.562612574</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>838204.2916604452</v>
+        <v>838204.2916604228</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         <v>469495.24</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>420493.7043095827</v>
+        <v>420493.7043095912</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>518496.7756904173</v>
+        <v>518496.7756904088</v>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         <v>155032.2310451691</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>72786.62044620635</v>
+        <v>72786.62044620622</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>237277.8416441319</v>
+        <v>237277.841644132</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         <v>-0.08620652940640688</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>1501650.892563412</v>
+        <v>1501656.193898288</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>1382431.279703259</v>
+        <v>1382439.134181864</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1620870.505423565</v>
+        <v>1620873.253614711</v>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
@@ -898,10 +898,10 @@
         <v>5964319.588486933</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>5714320.541844915</v>
+        <v>5714320.541844958</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>6214318.635128952</v>
+        <v>6214318.635128908</v>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
@@ -1374,16 +1374,16 @@
         <v>3835106.48</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>2050977.337103397</v>
+        <v>2050977.337103771</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>5886083.817103397</v>
+        <v>5886083.817103771</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>6050772.48</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>-164688.6628966024</v>
+        <v>-164688.662896229</v>
       </c>
     </row>
     <row r="6">
@@ -1428,16 +1428,16 @@
         <v>1329769.14</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>996020.4606607988</v>
+        <v>996020.4606608009</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2325789.600660799</v>
+        <v>2325789.600660801</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>3306890.82</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-981101.2193392008</v>
+        <v>-981101.2193391989</v>
       </c>
     </row>
     <row r="8">
@@ -1455,16 +1455,16 @@
         <v>1316036.09</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>742293.7866580579</v>
+        <v>742293.7866580297</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2058329.876658058</v>
+        <v>2058329.87665803</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>2002180.56</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>56149.31665805797</v>
+        <v>56149.3166580298</v>
       </c>
     </row>
     <row r="9">
@@ -1482,16 +1482,16 @@
         <v>581292.79</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>133883.6603217578</v>
+        <v>133883.660321754</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>715176.4503217579</v>
+        <v>715176.450321754</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>327602.52</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>387573.9303217579</v>
+        <v>387573.930321754</v>
       </c>
     </row>
     <row r="10">
@@ -1509,16 +1509,16 @@
         <v>1037069.78</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>594327.1133585527</v>
+        <v>594327.1133584343</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>1631396.893358553</v>
+        <v>1631396.893358434</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1487038.5</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>144358.3933585528</v>
+        <v>144358.3933584343</v>
       </c>
     </row>
     <row r="11">
@@ -1536,7 +1536,7 @@
         <v>1188753.1</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>630418.197614918</v>
+        <v>630418.1976149178</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>1819171.297614918</v>
@@ -1545,7 +1545,7 @@
         <v>1510361.92</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>308809.3776149182</v>
+        <v>308809.3776149179</v>
       </c>
     </row>
     <row r="12">
@@ -1590,16 +1590,16 @@
         <v>2267507.96</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1656841.826636346</v>
+        <v>1656841.82663635</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>3924349.786636346</v>
+        <v>3924349.78663635</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>3840693.77</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>83656.016636346</v>
+        <v>83656.01663634973</v>
       </c>
     </row>
     <row r="14">
@@ -1644,16 +1644,16 @@
         <v>2131870.47</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1113332.849803158</v>
+        <v>1113332.849803169</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>3245203.319803158</v>
+        <v>3245203.319803169</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>3205113.2</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>40090.11980315764</v>
+        <v>40090.11980316928</v>
       </c>
     </row>
     <row r="16">
@@ -1671,16 +1671,16 @@
         <v>11646249.62</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>6140118.898362631</v>
+        <v>6140315.193825455</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>17786368.51836263</v>
+        <v>17786564.81382546</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>19147215.11</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>-1360846.591637366</v>
+        <v>-1360650.296174541</v>
       </c>
     </row>
     <row r="17">
@@ -1725,16 +1725,16 @@
         <v>2674900.71</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1399033.290616463</v>
+        <v>1399033.290616464</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>4073934.000616463</v>
+        <v>4073934.000616464</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>4476147.62</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>-402213.6193835367</v>
+        <v>-402213.6193835363</v>
       </c>
     </row>
     <row r="19">
@@ -1752,7 +1752,7 @@
         <v>1754956.39</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>887834.5045890469</v>
+        <v>887834.5045890471</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>2642790.894589047</v>
@@ -1779,16 +1779,16 @@
         <v>1720395.23</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>868442.196775842</v>
+        <v>868442.1967758432</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2588837.426775842</v>
+        <v>2588837.426775843</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>2954942.06</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>-366104.6332241581</v>
+        <v>-366104.6332241572</v>
       </c>
     </row>
     <row r="21">
@@ -1806,16 +1806,16 @@
         <v>5983806.13</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>3214492.434545765</v>
+        <v>3214492.434545761</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>9198298.564545766</v>
+        <v>9198298.564545762</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>9871045.23</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>-672746.6654542349</v>
+        <v>-672746.6654542387</v>
       </c>
     </row>
     <row r="22">
@@ -1833,16 +1833,16 @@
         <v>1127977.86</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>666531.643536928</v>
+        <v>666531.6435369272</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>1794509.503536928</v>
+        <v>1794509.503536927</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>1661106.94</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>133402.563536928</v>
+        <v>133402.5635369273</v>
       </c>
     </row>
     <row r="23">
@@ -1887,16 +1887,16 @@
         <v>346922.18</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>171284.1383220731</v>
+        <v>171284.1383220756</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>518206.3183220731</v>
+        <v>518206.3183220756</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>578932.39</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>-60726.07167792693</v>
+        <v>-60726.07167792437</v>
       </c>
     </row>
     <row r="25">
@@ -1914,16 +1914,16 @@
         <v>174810.39</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>101025.9273889406</v>
+        <v>101025.9273889296</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>275836.3173889407</v>
+        <v>275836.3173889297</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>270264.69</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>5571.627388940658</v>
+        <v>5571.627388929657</v>
       </c>
     </row>
     <row r="26">
@@ -1941,16 +1941,16 @@
         <v>1510035.48</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>167781.7158303749</v>
+        <v>167780.2793624432</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>1677817.195830375</v>
+        <v>1677815.759362443</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>1699211.2</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>-21394.004169625</v>
+        <v>-21395.44063755684</v>
       </c>
     </row>
     <row r="27">
@@ -1968,16 +1968,16 @@
         <v>128265.45</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>66030.45584340673</v>
+        <v>67410.53748287656</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>194295.9058434067</v>
+        <v>195675.9874828766</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>219606.58</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-25310.67415659325</v>
+        <v>-23930.59251712341</v>
       </c>
     </row>
     <row r="28">
@@ -1995,16 +1995,16 @@
         <v>20984.27</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>12679.9202871499</v>
+        <v>12679.92039912507</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>33664.1902871499</v>
+        <v>33664.19039912507</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>33808.07</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>-143.8797128500955</v>
+        <v>-143.8796008749268</v>
       </c>
     </row>
     <row r="29">
@@ -2049,16 +2049,16 @@
         <v>833695.67</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>356767.7276614694</v>
+        <v>356767.7350432953</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>1190463.397661469</v>
+        <v>1190463.405043295</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>1314296.54</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>-123833.1423385306</v>
+        <v>-123833.1349567047</v>
       </c>
     </row>
     <row r="31">
@@ -2076,16 +2076,16 @@
         <v>6845626.79</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>3433684.683326203</v>
+        <v>3433684.68332621</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>10279311.4733262</v>
+        <v>10279311.47332621</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>8750693.6</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>1528617.873326203</v>
+        <v>1528617.87332621</v>
       </c>
     </row>
   </sheetData>
